--- a/EKG_Kalite_Yönetim_Sistemi/04_Parça ve Proses Kontrolü/02_PPC2 - MSA, Kalibrasyon ve SPC/EKG-KLT-LST-01_olcum_aletleri_ve_kalibrasyon_listesi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/04_Parça ve Proses Kontrolü/02_PPC2 - MSA, Kalibrasyon ve SPC/EKG-KLT-LST-01_olcum_aletleri_ve_kalibrasyon_listesi.xlsx
@@ -1197,7 +1197,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-LST-01&amp;C&amp;"Arial,Regular"&amp;11Ölçüm Aletleri ve Kalibrasyon Listesi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 21.09.2026
+Revizyon nedeni: Mevcut cihaz kayıtları korunarak vade, rapor ve yetkili kullanım kararı alanları eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>